--- a/research/display_optimization/behavior_tree_display_optimization_methods.xlsx
+++ b/research/display_optimization/behavior_tree_display_optimization_methods.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Optimization Methods" sheetId="1" r:id="R6e2b32e01ae74d7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="2" r:id="R8d689e269e024e12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Optimization Methods" sheetId="1" r:id="R455433fe70dd4254"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="2" r:id="Ra632f04e331e4ca0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -374,7 +374,7 @@
         <x:v>鼠标附近看不清，但又不想整体放大</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>鼠标附近节点放大，远处节点保持上下文；当前插件已实现第一版</x:v>
+        <x:v>鼠标附近节点放大，远处节点保持上下文；当前最大倍率 1.20x</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
         <x:v>Medium</x:v>
@@ -383,7 +383,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
-        <x:v>Done / Improve Later</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="G4" s="10" t="str">
         <x:v>Good for large behavior trees because it preserves global context while enlarging local detail.</x:v>
@@ -400,7 +400,7 @@
         <x:v>节点太多，整棵树铺满屏幕</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>给每个节点加折叠按钮，把子树压缩成 summary node，并显示子节点数量</x:v>
+        <x:v>折叠子树并显示隐藏节点数量与两层摘要</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
         <x:v>Medium</x:v>
@@ -409,7 +409,7 @@
         <x:v>Very High</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
-        <x:v>Recommended Next</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="G5" s="10" t="str">
         <x:v>Directly addresses behavior tree readability and matches large-network complexity management research.</x:v>
@@ -426,7 +426,7 @@
         <x:v>节点卡片太大，同屏显示节点太少</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>节点只显示标题、类型、状态；详细参数放到 Inspector 或悬浮详情</x:v>
+        <x:v>节点只显示短标题和类型颜色；详细参数保留在 Inspector</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
         <x:v>Low</x:v>
@@ -435,7 +435,7 @@
         <x:v>Very High</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>Recommended Next</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="G6" s="10" t="str">
         <x:v>Fast to implement and easy to explain in the graduation project as a readability improvement.</x:v>
@@ -452,7 +452,7 @@
         <x:v>Live Debug 时不知道 NPC 正在执行哪条链</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
-        <x:v>高亮 Root 到当前执行节点的整条链，其他分支变暗</x:v>
+        <x:v>高亮 Root 到当前执行节点的整条链并显示叶节点状态</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
         <x:v>Low</x:v>
@@ -461,7 +461,7 @@
         <x:v>Very High</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
-        <x:v>Recommended Next</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="G7" s="10" t="str">
         <x:v>Strongly supports behavior tree debugging and makes the plugin feel closer to UE behavior tree debugging.</x:v>
@@ -487,7 +487,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="F8" s="11" t="str">
-        <x:v>Recommended Next</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="G8" s="10" t="str">
         <x:v>Pairs well with active path highlight and is simple to validate visually.</x:v>
@@ -504,7 +504,7 @@
         <x:v>一个 Selector 或 Sequence 有很多子节点时横向太长</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>同一父节点下超过 N 个子节点时自动分成多列，同时用编号保留从左到右执行顺序</x:v>
+        <x:v>宽扇出分支自动分列，同时保留从左到右执行顺序</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
         <x:v>Medium</x:v>
@@ -513,7 +513,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="F9" s="11" t="str">
-        <x:v>Recommended</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="G9" s="10" t="str">
         <x:v>Supported by large fan-out tree visualization research; useful when selectors have many actions.</x:v>
@@ -530,7 +530,7 @@
         <x:v>用户在大树中迷路</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
-        <x:v>强化 GraphEdit minimap，支持点击定位、显示当前视口和当前执行节点</x:v>
+        <x:v>230x150 小地图显示全部节点、当前视口和运行状态</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
         <x:v>Medium</x:v>
@@ -539,7 +539,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="F10" s="11" t="str">
-        <x:v>Optional</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="G10" s="10" t="str">
         <x:v>Useful for navigation, but less central than collapse or active path highlighting.</x:v>
@@ -556,7 +556,7 @@
         <x:v>缩小时文字看不清，放大后信息又太多</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
-        <x:v>缩小时只显示类型颜色和短标题，放大后显示参数、描述、Decorator 条件</x:v>
+        <x:v>缩小时逐级隐藏次要字段，放大后显示参数、描述和 Decorator</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
         <x:v>Medium</x:v>
@@ -565,7 +565,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="F11" s="11" t="str">
-        <x:v>Recommended</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="G11" s="10" t="str">
         <x:v>Works naturally with GraphEdit zoom and can be described as multi-scale visualization.</x:v>
@@ -582,7 +582,7 @@
         <x:v>大树里只想快速知道当前执行链</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
-        <x:v>顶部显示 Root &gt; Selector &gt; Attack Left，点击路径项可跳转节点</x:v>
+        <x:v>顶部显示可点击的运行链并跳转节点</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
         <x:v>Low</x:v>
@@ -591,7 +591,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="F12" s="11" t="str">
-        <x:v>Recommended Next</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="G12" s="10" t="str">
         <x:v>Simple and very useful for live debugging; complements visual highlighting.</x:v>
@@ -608,7 +608,7 @@
         <x:v>判断条件藏在 JSON 参数里，不直观</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
-        <x:v>在节点顶部显示 IF player_in_range == true、Cooldown 1.5s 等标签</x:v>
+        <x:v>在节点卡片显示黑板条件、Cooldown 和 Time Limit 摘要</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
         <x:v>Low</x:v>
@@ -617,7 +617,7 @@
         <x:v>Very High</x:v>
       </x:c>
       <x:c r="F13" s="11" t="str">
-        <x:v>Recommended Next</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="G13" s="10" t="str">
         <x:v>Makes behavior tree logic readable without opening the inspector.</x:v>
@@ -634,7 +634,7 @@
         <x:v>大树中找节点、Action 或 blackboard key 困难</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>搜索节点标题、Action 方法名、blackboard key，并高亮/跳转结果</x:v>
+        <x:v>搜索标题、类型、描述、方法和参数，并高亮/跳转结果</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
         <x:v>Low</x:v>
@@ -643,7 +643,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="F14" s="11" t="str">
-        <x:v>Recommended</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="G14" s="10" t="str">
         <x:v>High usability gain with low implementation cost.</x:v>
@@ -660,7 +660,7 @@
         <x:v>曲线连接太多时上下关系不清楚</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
-        <x:v>使用 UE 蓝图风格的直角折线连接，减少线条歧义</x:v>
+        <x:v>使用直角折线连接降低层次关系歧义</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
         <x:v>Medium</x:v>
@@ -669,7 +669,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="F15" s="11" t="str">
-        <x:v>Optional</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="G15" s="10" t="str">
         <x:v>Improves UE-like appearance, but may require custom connection drawing.</x:v>
@@ -686,7 +686,7 @@
         <x:v>大量连线互相遮挡</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
-        <x:v>同方向、同父节点或同类型连线进行捆绑/合并显示</x:v>
+        <x:v>同父同向连线共享主干以降低视觉噪声</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
         <x:v>High</x:v>
@@ -695,7 +695,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="F16" s="11" t="str">
-        <x:v>Research Extension</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="G16" s="10" t="str">
         <x:v>More useful for dense graphs than pure trees; good as an advanced discussion point.</x:v>
@@ -712,7 +712,7 @@
         <x:v>每次自动排列后节点大幅跳动，用户失去空间记忆</x:v>
       </x:c>
       <x:c r="C17" s="10" t="str">
-        <x:v>自动布局时尽量保持已有节点位置，只调整新增节点或重叠节点</x:v>
+        <x:v>自动布局尽量保留已有节点位置，只处理冲突节点</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
         <x:v>Medium</x:v>
@@ -721,7 +721,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="F17" s="11" t="str">
-        <x:v>Recommended</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="G17" s="10" t="str">
         <x:v>Important for preserving the user's mental map when editing large trees.</x:v>
@@ -738,7 +738,7 @@
         <x:v>选中深层节点后不知道它属于哪个分支</x:v>
       </x:c>
       <x:c r="C18" s="10" t="str">
-        <x:v>显示当前选择节点路径：Root / Patrol / Move Left</x:v>
+        <x:v>显示选中节点祖先路径并支持点击跳转</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
         <x:v>Low</x:v>
@@ -747,7 +747,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="F18" s="11" t="str">
-        <x:v>Optional</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="G18" s="10" t="str">
         <x:v>Simple navigation aid, especially useful after subtree collapse is added.</x:v>
@@ -764,7 +764,7 @@
         <x:v>Decorator 失败后不知道为什么</x:v>
       </x:c>
       <x:c r="C19" s="10" t="str">
-        <x:v>Live Debug 显示 player_in_range failed、cooldown active 等失败原因</x:v>
+        <x:v>Live Debug 标注 FAILURE 节点和具体失败原因</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
         <x:v>Medium</x:v>
@@ -773,7 +773,7 @@
         <x:v>Very High</x:v>
       </x:c>
       <x:c r="F19" s="11" t="str">
-        <x:v>Recommended Next</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="G19" s="10" t="str">
         <x:v>Directly improves runtime debugging and demonstrates behavior tree execution transparency.</x:v>
@@ -794,12 +794,12 @@
       <x:formula1>"Medium,High,Very High"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="F4:F19">
-      <x:formula1>"Done / Improve Later,Recommended Next,Recommended,Optional,Research Extension"</x:formula1>
+      <x:formula1>"Completed,Improve Later,Optional,Research Extension"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R465be780502c4232"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra112277a717146ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -909,7 +909,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32e419a025d745a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4db5b3ded954780"/>
   </x:tableParts>
 </x:worksheet>
 </file>